--- a/data/opponent_team.xlsx
+++ b/data/opponent_team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1794" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C340071-8C29-4734-A8F8-C20588DC98BA}"/>
+  <xr:revisionPtr revIDLastSave="1799" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6195210-D7A6-4817-8407-0F2BD377EE8A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Animus" sheetId="1" r:id="rId1"/>
@@ -1129,13 +1129,13 @@
     <t>Team_name</t>
   </si>
   <si>
-    <t>火 Gokai</t>
-  </si>
-  <si>
     <t>Server</t>
   </si>
   <si>
     <t>Global</t>
+  </si>
+  <si>
+    <t>火 Gokai (Buff: Increase Turn Meter)</t>
   </si>
 </sst>
 </file>
@@ -2704,7 +2704,7 @@
         <v>89</v>
       </c>
       <c r="C1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -2712,10 +2712,10 @@
         <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/data/opponent_team.xlsx
+++ b/data/opponent_team.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1799" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6195210-D7A6-4817-8407-0F2BD377EE8A}"/>
+  <xr:revisionPtr revIDLastSave="1934" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{429F7AEF-22B3-4E03-82A4-917C0A58508E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Animus" sheetId="1" r:id="rId1"/>
     <sheet name="Opponent_Team" sheetId="11" r:id="rId2"/>
     <sheet name="W019" sheetId="10" r:id="rId3"/>
+    <sheet name="W020" sheetId="12" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="81">
+  <futureMetadata name="XLRICHVALUE" count="83">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -607,8 +608,22 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="81"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="82"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="81">
+  <valueMetadata count="83">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -851,13 +866,19 @@
     </bk>
     <bk>
       <rc t="1" v="80"/>
+    </bk>
+    <bk>
+      <rc t="1" v="81"/>
+    </bk>
+    <bk>
+      <rc t="1" v="82"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="96">
   <si>
     <t>Animus</t>
   </si>
@@ -1132,10 +1153,19 @@
     <t>Server</t>
   </si>
   <si>
-    <t>Global</t>
-  </si>
-  <si>
     <t>火 Gokai (Buff: Increase Turn Meter)</t>
+  </si>
+  <si>
+    <t>Auroral Nell</t>
+  </si>
+  <si>
+    <t>Syen</t>
+  </si>
+  <si>
+    <t>W020</t>
+  </si>
+  <si>
+    <t>TheStars (Buff: Heal)</t>
   </si>
 </sst>
 </file>
@@ -1145,7 +1175,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmmm\ yyyy"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1175,6 +1205,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1310,7 +1346,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="81">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="83">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1633,6 +1669,14 @@
   </rv>
   <rv s="0">
     <v>80</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>81</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>82</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -1730,6 +1774,8 @@
   <rel r:id="rId79"/>
   <rel r:id="rId80"/>
   <rel r:id="rId81"/>
+  <rel r:id="rId82"/>
+  <rel r:id="rId83"/>
 </richValueRels>
 </file>
 
@@ -2018,7 +2064,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B84"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" style="9" customWidth="1"/>
@@ -2061,7 +2107,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="B5" s="2" t="e" vm="4">
         <v>#VALUE!</v>
@@ -2069,7 +2115,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="e" vm="5">
         <v>#VALUE!</v>
@@ -2077,7 +2123,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="e" vm="6">
         <v>#VALUE!</v>
@@ -2085,23 +2131,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="5" t="e" vm="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="2" t="e" vm="8">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="e" vm="9">
         <v>#VALUE!</v>
@@ -2109,7 +2155,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="e" vm="10">
         <v>#VALUE!</v>
@@ -2117,7 +2163,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="e" vm="11">
         <v>#VALUE!</v>
@@ -2125,23 +2171,23 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="2" t="e" vm="12">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="B14" s="2" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B14" s="2" t="e" vm="13">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="B15" s="2" t="e" vm="14">
         <v>#VALUE!</v>
@@ -2149,7 +2195,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="e" vm="15">
         <v>#VALUE!</v>
@@ -2157,7 +2203,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="e" vm="16">
         <v>#VALUE!</v>
@@ -2165,7 +2211,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="e" vm="17">
         <v>#VALUE!</v>
@@ -2173,7 +2219,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="e" vm="18">
         <v>#VALUE!</v>
@@ -2181,7 +2227,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="e" vm="19">
         <v>#VALUE!</v>
@@ -2189,7 +2235,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="e" vm="20">
         <v>#VALUE!</v>
@@ -2197,7 +2243,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="e" vm="21">
         <v>#VALUE!</v>
@@ -2205,7 +2251,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="e" vm="22">
         <v>#VALUE!</v>
@@ -2213,7 +2259,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="e" vm="23">
         <v>#VALUE!</v>
@@ -2221,7 +2267,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="e" vm="24">
         <v>#VALUE!</v>
@@ -2229,7 +2275,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="e" vm="25">
         <v>#VALUE!</v>
@@ -2237,7 +2283,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2" t="e" vm="26">
         <v>#VALUE!</v>
@@ -2245,31 +2291,31 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="7" t="e" vm="27">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+      <c r="B29" s="7" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="7" t="e" vm="28">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="e" vm="29">
+      <c r="B30" s="7" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2" t="e" vm="30">
         <v>#VALUE!</v>
@@ -2277,7 +2323,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="2" t="e" vm="31">
         <v>#VALUE!</v>
@@ -2285,7 +2331,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="2" t="e" vm="32">
         <v>#VALUE!</v>
@@ -2293,23 +2339,23 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="7" t="e" vm="33">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="e" vm="33">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="2" t="e" vm="34">
+        <v>85</v>
+      </c>
+      <c r="B35" s="7" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36" s="2" t="e" vm="35">
         <v>#VALUE!</v>
@@ -2317,7 +2363,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37" s="2" t="e" vm="36">
         <v>#VALUE!</v>
@@ -2325,7 +2371,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" s="2" t="e" vm="37">
         <v>#VALUE!</v>
@@ -2333,7 +2379,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" s="2" t="e" vm="38">
         <v>#VALUE!</v>
@@ -2341,7 +2387,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" s="2" t="e" vm="39">
         <v>#VALUE!</v>
@@ -2349,7 +2395,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="2" t="e" vm="40">
         <v>#VALUE!</v>
@@ -2357,7 +2403,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="2" t="e" vm="41">
         <v>#VALUE!</v>
@@ -2365,7 +2411,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" s="2" t="e" vm="42">
         <v>#VALUE!</v>
@@ -2373,7 +2419,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B44" s="2" t="e" vm="43">
         <v>#VALUE!</v>
@@ -2381,7 +2427,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B45" s="2" t="e" vm="44">
         <v>#VALUE!</v>
@@ -2389,7 +2435,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B46" s="2" t="e" vm="45">
         <v>#VALUE!</v>
@@ -2397,23 +2443,23 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="2" t="e" vm="46">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="2" t="e" vm="46">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
+      <c r="B48" s="2" t="e" vm="47">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="B48" s="2" t="e" vm="47">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="B49" s="2" t="e" vm="48">
         <v>#VALUE!</v>
@@ -2421,7 +2467,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B50" s="2" t="e" vm="49">
         <v>#VALUE!</v>
@@ -2429,7 +2475,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B51" s="2" t="e" vm="50">
         <v>#VALUE!</v>
@@ -2437,7 +2483,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B52" s="2" t="e" vm="51">
         <v>#VALUE!</v>
@@ -2445,31 +2491,31 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B53" s="8" t="e" vm="52">
+        <v>50</v>
+      </c>
+      <c r="B53" s="2" t="e" vm="52">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B54" s="8" t="e" vm="53">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="2" t="e" vm="53">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
+      <c r="B55" s="2" t="e" vm="54">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="B55" s="2" t="e" vm="54">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="B56" s="2" t="e" vm="55">
         <v>#VALUE!</v>
@@ -2477,7 +2523,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B57" s="2" t="e" vm="56">
         <v>#VALUE!</v>
@@ -2485,7 +2531,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B58" s="2" t="e" vm="57">
         <v>#VALUE!</v>
@@ -2493,7 +2539,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B59" s="2" t="e" vm="58">
         <v>#VALUE!</v>
@@ -2501,7 +2547,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B60" s="2" t="e" vm="59">
         <v>#VALUE!</v>
@@ -2509,7 +2555,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B61" s="2" t="e" vm="60">
         <v>#VALUE!</v>
@@ -2517,7 +2563,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B62" s="2" t="e" vm="61">
         <v>#VALUE!</v>
@@ -2525,7 +2571,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B63" s="2" t="e" vm="62">
         <v>#VALUE!</v>
@@ -2533,7 +2579,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B64" s="2" t="e" vm="63">
         <v>#VALUE!</v>
@@ -2541,7 +2587,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B65" s="2" t="e" vm="64">
         <v>#VALUE!</v>
@@ -2549,7 +2595,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B66" s="2" t="e" vm="65">
         <v>#VALUE!</v>
@@ -2557,7 +2603,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B67" s="2" t="e" vm="66">
         <v>#VALUE!</v>
@@ -2565,7 +2611,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B68" s="2" t="e" vm="67">
         <v>#VALUE!</v>
@@ -2573,15 +2619,15 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B69" s="2" t="e" vm="68">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="4" t="s">
-        <v>68</v>
+      <c r="A70" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B70" s="2" t="e" vm="69">
         <v>#VALUE!</v>
@@ -2589,15 +2635,15 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B71" s="2" t="e" vm="70">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
-        <v>70</v>
+      <c r="A72" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="B72" s="2" t="e" vm="71">
         <v>#VALUE!</v>
@@ -2605,7 +2651,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B73" s="2" t="e" vm="72">
         <v>#VALUE!</v>
@@ -2613,7 +2659,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B74" s="2" t="e" vm="73">
         <v>#VALUE!</v>
@@ -2621,7 +2667,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B75" s="2" t="e" vm="74">
         <v>#VALUE!</v>
@@ -2629,7 +2675,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B76" s="2" t="e" vm="75">
         <v>#VALUE!</v>
@@ -2637,7 +2683,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B77" s="2" t="e" vm="76">
         <v>#VALUE!</v>
@@ -2645,7 +2691,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B78" s="2" t="e" vm="77">
         <v>#VALUE!</v>
@@ -2653,15 +2699,15 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B79" s="5" t="e" vm="78">
+        <v>75</v>
+      </c>
+      <c r="B79" s="2" t="e" vm="78">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B80" s="2" t="e" vm="79">
         <v>#VALUE!</v>
@@ -2669,17 +2715,33 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B81" s="2" t="e" vm="80">
+        <v>77</v>
+      </c>
+      <c r="B81" s="5" t="e" vm="80">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B82" s="2" t="e" vm="81">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B83" s="2" t="e" vm="82">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B82" s="2" t="e" vm="81">
+      <c r="B84" s="2" t="e" vm="83">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -2693,7 +2755,7 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -2712,14 +2774,17 @@
         <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C2" s="10" t="s">
         <v>91</v>
       </c>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="11"/>
+      <c r="A3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" t="s">
+        <v>95</v>
+      </c>
       <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2787,6 +2852,7 @@
       <c r="C19" s="10"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3228,7 +3294,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8F897EBC-B8DA-4BC0-B921-3E52283D36DC}">
           <x14:formula1>
-            <xm:f>Animus!$A$2:$A$82</xm:f>
+            <xm:f>Animus!$A$2:$A$84</xm:f>
           </x14:formula1>
           <xm:sqref>A2:C30</xm:sqref>
         </x14:dataValidation>
@@ -3236,4 +3302,390 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5509B12-9FCD-4D34-A6B0-B0D80DA48440}">
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5473D153-867E-4A9F-A78A-CD745F5A533C}">
+          <x14:formula1>
+            <xm:f>Animus!$A$2:$A$84</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:C26</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
 </file>